--- a/testData/Test_Orchestration.xlsx
+++ b/testData/Test_Orchestration.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB5A106-0277-4219-8033-5B3DCCD0C75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{0CB5A106-0277-4219-8033-5B3DCCD0C75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{853AE86C-7653-4F90-A47F-B38EEC059466}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$22</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>Test Name</t>
   </si>
@@ -253,6 +253,16 @@
   </si>
   <si>
     <t>This test script automates the process of logging into Salesforce, creating a Direct opportunity, configuring a Keystone product(Keystone Storage-as-a-Service v3), updating its details in the Account Information, GTC Risks, Approval Request, Attachments, and Purchase Order tabs, and validating the quote status by approving the quote in TPD.</t>
+  </si>
+  <si>
+    <t>TC_E_EF_Series_Regression</t>
+  </si>
+  <si>
+    <t>Regression test for E/EF-Series product</t>
+  </si>
+  <si>
+    <t>This test script performs regression testing for the E/EF-Series product across different scenarios including opportunity creation, quote creation, product configuration, order submission and validating the quote status by approving the quote in TPD. 
+The test iterates through multiple sets of test data to validate various functionalities and configurations of the E/EF-Series product in the CPQ system.</t>
   </si>
 </sst>
 </file>
@@ -674,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.15234375" customWidth="1"/>
@@ -719,219 +729,219 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
+    <row r="7" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>43</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
+      <c r="A9" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="2"/>
+        <v>46</v>
+      </c>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>24</v>
+      <c r="A10" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
-        <v>26</v>
+      <c r="A11" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>3</v>
@@ -940,129 +950,144 @@
         <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" ht="87.45" x14ac:dyDescent="0.4">
-      <c r="A23" s="4" t="s">
-        <v>70</v>
+    <row r="23" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>57</v>
+      <c r="C23" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>8</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>30</v>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A25" s="4" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
-        <v>38</v>
+      <c r="A26" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="43.75" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -1070,7 +1095,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:B26">
+  <conditionalFormatting sqref="B4:B27">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"No"</formula>
     </cfRule>
@@ -1079,7 +1104,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B26" xr:uid="{A3790C04-5599-453D-8668-8A2767811604}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B27" xr:uid="{0EAD7C8F-4E47-46C3-8259-CF9662006082}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
